--- a/dev/build/encoding-prep/aero-cou2/aero-cou2-extracted.xlsx
+++ b/dev/build/encoding-prep/aero-cou2/aero-cou2-extracted.xlsx
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1520,14 +1520,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -1580,7 +1572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1687,7 +1679,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>cou_definition.docx; cfx_solver_settings.txt; EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cfx_solver_settings.txt; cou_definition.docx</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1701,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>cou_definition.docx; cfx_solver_settings.txt; EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cascade_reuse_traceability.txt</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1723,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>cou_definition.docx; cfx_solver_settings.txt; EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cruise_uq_study.csv</t>
         </is>
       </c>
     </row>
@@ -1753,14 +1745,10 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>cou_definition.docx; cfx_solver_settings.txt; EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
+          <t>sensitivity_study_cruise.csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
@@ -2123,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2208,11 +2196,7 @@
           <t>ValidationResult</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Stable URI or local ID</t>
-        </is>
-      </c>
+      <c r="C3" s="3" t="n"/>
       <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Method of manufactured solutions benchmark verification of the ANSYS CFX solver, inherited unchanged from COU1 since no model form or numerics changes were made for cruise.</t>
@@ -2287,7 +2271,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx; the study CSVs named in EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cascade_reuse_traceability.txt; credibility_assessment_narrative.docx §1.3</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2313,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx; the study CSVs named in EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cascade_reuse_traceability.txt (primary evidence); credibility_assessment_narrative.docx §4.2 (assessment)</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2360,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx; the study CSVs named in EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cruise_uq_study.csv (primary evidence); credibility_assessment_narrative.docx §5.4 (assessment)</t>
         </is>
       </c>
     </row>
@@ -2418,14 +2402,10 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx; the study CSVs named in EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
+          <t>sensitivity_study_cruise.csv (primary evidence); credibility_assessment_narrative.docx §5.5 (assessment)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
@@ -2441,7 +2421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2598,7 +2578,7 @@
       <c r="H5" s="10" t="n"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §1.1</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2617,7 @@
       <c r="H6" s="10" t="n"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §1.2</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2656,7 @@
       <c r="H7" s="10" t="n"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §1.3</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2695,7 @@
       <c r="H8" s="10" t="n"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cfx_solver_settings.txt (primary evidence); credibility_assessment_narrative.docx §1.4 (assessed level)</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2734,7 @@
       <c r="H9" s="10" t="n"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §1.5</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2771,7 @@
       <c r="H10" s="10" t="n"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §2.1</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2810,7 @@
       <c r="H11" s="10" t="n"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §2.2</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2849,7 @@
       <c r="H12" s="10" t="n"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §2.3</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2886,7 @@
       <c r="H13" s="10" t="n"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cascade_reuse_traceability.txt (primary evidence); credibility_assessment_narrative.docx §2.4 (assessed level)</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2923,7 @@
       <c r="H14" s="10" t="n"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §3.1</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2960,7 @@
       <c r="H15" s="10" t="n"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §3.2</t>
         </is>
       </c>
     </row>
@@ -3019,7 +2999,7 @@
       <c r="H16" s="10" t="n"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §4.1</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3025,7 @@
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>NASA-STD-7009B guidance requires the validation experiment to sample the operating envelope of the COU, and the cascade regime lies outside the cruise envelope, so the validation is not relevant and this factor is Not Assessed.</t>
+          <t>NASA-STD-7009B guidance requires the validation experiment to sample the operating envelope of the COU, and the cascade regime lies outside the cruise envelope, so the validation is not relevant and this factor is Not Assessed. DECLINED MAPPING: the source states a Film Cooling Validation gap at narrative §4.3 (Level 1 against Level 3 required), scoped by the source itself as inherited from COU1 rather than a COU2-specific finding. No pack factor expresses it. See AMBIGUITY_LOG G-06.</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -3056,7 +3036,7 @@
       <c r="H17" s="10" t="n"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §4.2; §6 open item 5</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3075,7 @@
       <c r="H18" s="10" t="n"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §5.1</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3114,7 @@
       <c r="H19" s="10" t="n"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>review_board_minutes_cruise_2026Q2.txt (primary evidence); credibility_assessment_narrative.docx §5.2 (assessed level)</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3153,7 @@
       <c r="H20" s="10" t="n"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §5.3</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3192,7 @@
       <c r="H21" s="10" t="n"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cruise_uq_study.csv (primary evidence); credibility_assessment_narrative.docx §5.4 (assessed level)</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3231,7 @@
       <c r="H22" s="10" t="n"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>sensitivity_study_cruise.csv (primary evidence); credibility_assessment_narrative.docx §5.5 (assessed level)</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3270,7 @@
       <c r="H23" s="10" t="n"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §5.6</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3391,14 +3371,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
